--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136274000</v>
       </c>
       <c r="B2" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136281160</v>
       </c>
       <c r="B22" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136281359</v>
       </c>
       <c r="B23" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>136281412</v>
       </c>
       <c r="B24" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>136281539</v>
       </c>
       <c r="B27" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136281443</v>
       </c>
       <c r="B28" t="n">
-        <v>57952</v>
+        <v>57954</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136274182</v>
       </c>
       <c r="B41" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136275420</v>
       </c>
       <c r="B42" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>136275005</v>
       </c>
       <c r="B44" t="n">
-        <v>56935</v>
+        <v>56937</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 21612-2026 artfynd.xlsx
+++ b/artfynd/A 21612-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>136274843</v>
       </c>
       <c r="B8" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>136281124</v>
       </c>
       <c r="B9" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>136281338</v>
       </c>
       <c r="B10" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136272895</v>
       </c>
       <c r="B19" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136280972</v>
       </c>
       <c r="B20" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136281386</v>
       </c>
       <c r="B21" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
